--- a/3학년 2학기/기인프/중간고사/[과제평가] 중간 시험 제출_기초인공지능프로그래밍_20261026.xlsx
+++ b/3학년 2학기/기인프/중간고사/[과제평가] 중간 시험 제출_기초인공지능프로그래밍_20261026.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Documents\GitHub\SOGANG\3학년 2학기\기인프\중간고사\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -84962,14 +84962,14 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -85269,34 +85269,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A2" s="7"/>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
+      <c r="A2" s="8"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
@@ -85373,12 +85373,13 @@
       <c r="L5" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="N5" s="1">
+      <c r="M5" s="1">
         <v>17</v>
       </c>
-      <c r="O5" s="8">
+      <c r="N5" s="6">
         <v>17</v>
       </c>
+      <c r="O5" s="6"/>
     </row>
     <row r="6" spans="1:15" ht="213.75" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
@@ -85417,12 +85418,13 @@
       <c r="L6" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="N6" s="1">
+      <c r="M6" s="1">
         <v>8</v>
       </c>
-      <c r="O6" s="8">
-        <v>7.5</v>
+      <c r="N6" s="6">
+        <v>3.75</v>
       </c>
+      <c r="O6" s="6"/>
     </row>
     <row r="7" spans="1:15" ht="213.75" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
@@ -85461,12 +85463,13 @@
       <c r="L7" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="N7" s="1">
+      <c r="M7" s="1">
         <v>13</v>
       </c>
-      <c r="O7" s="8">
+      <c r="N7" s="6">
         <v>13</v>
       </c>
+      <c r="O7" s="6"/>
     </row>
     <row r="8" spans="1:15" ht="213.75" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
@@ -85505,12 +85508,13 @@
       <c r="L8" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="N8" s="1">
+      <c r="M8" s="1">
         <v>17</v>
       </c>
-      <c r="O8" s="8">
+      <c r="N8" s="6">
         <v>17</v>
       </c>
+      <c r="O8" s="6"/>
     </row>
     <row r="9" spans="1:15" ht="213.75" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
@@ -85549,12 +85553,13 @@
       <c r="L9" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="N9" s="1">
+      <c r="M9" s="1">
         <v>12</v>
       </c>
-      <c r="O9" s="8">
-        <v>8.5</v>
+      <c r="N9" s="6">
+        <v>10.3</v>
       </c>
+      <c r="O9" s="6"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
@@ -85593,12 +85598,13 @@
       <c r="L10" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="N10" s="1">
+      <c r="M10" s="1">
         <v>0</v>
       </c>
-      <c r="O10" s="8">
+      <c r="N10" s="6">
         <v>0</v>
       </c>
+      <c r="O10" s="6"/>
     </row>
     <row r="11" spans="1:15" ht="213.75" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
@@ -85637,12 +85643,13 @@
       <c r="L11" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="N11" s="1">
+      <c r="M11" s="1">
         <v>17</v>
       </c>
-      <c r="O11" s="8">
+      <c r="N11" s="6">
         <v>17</v>
       </c>
+      <c r="O11" s="6"/>
     </row>
     <row r="12" spans="1:15" ht="242.25" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
@@ -85681,12 +85688,13 @@
       <c r="L12" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="N12" s="1">
+      <c r="M12" s="1">
         <v>4.5</v>
       </c>
-      <c r="O12" s="8">
+      <c r="N12" s="6">
         <v>7.25</v>
       </c>
+      <c r="O12" s="6"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
@@ -85725,12 +85733,13 @@
       <c r="L13" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="N13" s="1">
+      <c r="M13" s="1">
         <v>0</v>
       </c>
-      <c r="O13" s="8">
+      <c r="N13" s="6">
         <v>0</v>
       </c>
+      <c r="O13" s="6"/>
     </row>
     <row r="14" spans="1:15" ht="213.75" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
@@ -85769,12 +85778,13 @@
       <c r="L14" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="N14" s="1">
+      <c r="M14" s="1">
         <v>17</v>
       </c>
-      <c r="O14" s="8">
+      <c r="N14" s="6">
         <v>17</v>
       </c>
+      <c r="O14" s="6"/>
     </row>
     <row r="15" spans="1:15" ht="213.75" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
@@ -85813,12 +85823,13 @@
       <c r="L15" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="N15" s="1">
+      <c r="M15" s="1">
         <v>17</v>
       </c>
-      <c r="O15" s="8">
+      <c r="N15" s="6">
         <v>17</v>
       </c>
+      <c r="O15" s="6"/>
     </row>
     <row r="16" spans="1:15" ht="213.75" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
@@ -85857,12 +85868,13 @@
       <c r="L16" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="N16" s="1">
+      <c r="M16" s="1">
         <v>14</v>
       </c>
-      <c r="O16" s="8">
+      <c r="N16" s="6">
         <v>14</v>
       </c>
+      <c r="O16" s="6"/>
     </row>
     <row r="17" spans="1:15" ht="213.75" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
@@ -85901,12 +85913,13 @@
       <c r="L17" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="N17" s="1">
+      <c r="M17" s="1">
         <v>2</v>
       </c>
-      <c r="O17" s="8">
+      <c r="N17" s="6">
         <v>1</v>
       </c>
+      <c r="O17" s="6"/>
     </row>
     <row r="18" spans="1:15" ht="213.75" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
@@ -85945,12 +85958,13 @@
       <c r="L18" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="N18" s="1">
+      <c r="M18" s="1">
         <v>16</v>
       </c>
-      <c r="O18" s="8">
+      <c r="N18" s="6">
         <v>15</v>
       </c>
+      <c r="O18" s="6"/>
     </row>
     <row r="19" spans="1:15" ht="242.25" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
@@ -85989,12 +86003,13 @@
       <c r="L19" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="N19" s="1">
+      <c r="M19" s="1">
         <v>4.625</v>
       </c>
-      <c r="O19" s="8">
-        <v>9.25</v>
+      <c r="N19" s="6">
+        <v>4.625</v>
       </c>
+      <c r="O19" s="6"/>
     </row>
     <row r="20" spans="1:15" ht="242.25" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
@@ -86033,12 +86048,13 @@
       <c r="L20" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="N20" s="1">
+      <c r="M20" s="1">
         <v>5.5</v>
       </c>
-      <c r="O20" s="8">
-        <v>12.5</v>
+      <c r="N20" s="6">
+        <v>6.25</v>
       </c>
+      <c r="O20" s="6"/>
     </row>
     <row r="21" spans="1:15" ht="213.75" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
@@ -86077,12 +86093,13 @@
       <c r="L21" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="N21" s="1">
+      <c r="M21" s="1">
         <v>1</v>
       </c>
-      <c r="O21" s="8">
+      <c r="N21" s="6">
         <v>0.5</v>
       </c>
+      <c r="O21" s="6"/>
     </row>
     <row r="22" spans="1:15" ht="213.75" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
@@ -86121,12 +86138,13 @@
       <c r="L22" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="N22" s="1">
+      <c r="M22" s="1">
         <v>14</v>
       </c>
-      <c r="O22" s="8">
+      <c r="N22" s="6">
         <v>13</v>
       </c>
+      <c r="O22" s="6"/>
     </row>
     <row r="23" spans="1:15" ht="213.75" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
@@ -86165,12 +86183,13 @@
       <c r="L23" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="N23" s="1">
+      <c r="M23" s="1">
         <v>0</v>
       </c>
-      <c r="O23" s="8">
+      <c r="N23" s="6">
         <v>0</v>
       </c>
+      <c r="O23" s="6"/>
     </row>
     <row r="24" spans="1:15" ht="213.75" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
@@ -86209,12 +86228,13 @@
       <c r="L24" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="N24" s="1">
+      <c r="M24" s="1">
         <v>5</v>
       </c>
-      <c r="O24" s="8">
-        <v>2</v>
+      <c r="N24" s="6">
+        <v>8</v>
       </c>
+      <c r="O24" s="6"/>
     </row>
     <row r="25" spans="1:15" ht="213.75" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
@@ -86253,12 +86273,13 @@
       <c r="L25" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="N25" s="1">
+      <c r="M25" s="1">
         <v>17</v>
       </c>
-      <c r="O25" s="8">
+      <c r="N25" s="6">
         <v>17</v>
       </c>
+      <c r="O25" s="6"/>
     </row>
     <row r="26" spans="1:15" ht="213.75" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
@@ -86297,12 +86318,13 @@
       <c r="L26" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="N26" s="1">
+      <c r="M26" s="1">
         <v>13.75</v>
       </c>
-      <c r="O26" s="8">
+      <c r="N26" s="6">
         <v>14.75</v>
       </c>
+      <c r="O26" s="6"/>
     </row>
     <row r="27" spans="1:15" ht="213.75" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
@@ -86341,12 +86363,13 @@
       <c r="L27" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="N27" s="1">
+      <c r="M27" s="1">
         <v>17</v>
       </c>
-      <c r="O27" s="8">
+      <c r="N27" s="6">
         <v>17</v>
       </c>
+      <c r="O27" s="6"/>
     </row>
     <row r="28" spans="1:15" ht="213.75" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
@@ -86385,12 +86408,13 @@
       <c r="L28" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="N28" s="1">
+      <c r="M28" s="1">
         <v>17</v>
       </c>
-      <c r="O28" s="8">
+      <c r="N28" s="6">
         <v>17</v>
       </c>
+      <c r="O28" s="6"/>
     </row>
     <row r="29" spans="1:15" ht="213.75" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
@@ -86429,12 +86453,13 @@
       <c r="L29" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="N29" s="1">
+      <c r="M29" s="1">
         <v>17</v>
       </c>
-      <c r="O29" s="8">
+      <c r="N29" s="6">
         <v>17</v>
       </c>
+      <c r="O29" s="6"/>
     </row>
     <row r="30" spans="1:15" ht="213.75" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
@@ -86473,12 +86498,13 @@
       <c r="L30" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="N30" s="1">
+      <c r="M30" s="1">
         <v>13.75</v>
       </c>
-      <c r="O30" s="8">
+      <c r="N30" s="6">
         <v>13.75</v>
       </c>
+      <c r="O30" s="6"/>
     </row>
     <row r="31" spans="1:15" ht="213.75" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
@@ -86517,12 +86543,13 @@
       <c r="L31" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="N31" s="1">
+      <c r="M31" s="1">
         <v>17</v>
       </c>
-      <c r="O31" s="8">
+      <c r="N31" s="6">
         <v>17</v>
       </c>
+      <c r="O31" s="6"/>
     </row>
     <row r="32" spans="1:15" ht="213.75" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
@@ -86561,12 +86588,13 @@
       <c r="L32" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="N32" s="1">
+      <c r="M32" s="1">
         <v>17</v>
       </c>
-      <c r="O32" s="8">
-        <v>16</v>
+      <c r="N32" s="6">
+        <v>14.8</v>
       </c>
+      <c r="O32" s="6"/>
     </row>
     <row r="33" spans="1:15" ht="213.75" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
@@ -86605,12 +86633,13 @@
       <c r="L33" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="N33" s="1">
+      <c r="M33" s="1">
         <v>17</v>
       </c>
-      <c r="O33" s="8">
+      <c r="N33" s="6">
         <v>17</v>
       </c>
+      <c r="O33" s="6"/>
     </row>
     <row r="34" spans="1:15" ht="213.75" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
@@ -86649,12 +86678,13 @@
       <c r="L34" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="N34" s="1">
+      <c r="M34" s="1">
         <v>17</v>
       </c>
-      <c r="O34" s="8">
+      <c r="N34" s="6">
         <v>17</v>
       </c>
+      <c r="O34" s="6"/>
     </row>
     <row r="35" spans="1:15" ht="242.25" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
@@ -86693,12 +86723,13 @@
       <c r="L35" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="N35" s="1">
+      <c r="M35" s="1">
         <v>3.875</v>
       </c>
-      <c r="O35" s="8">
-        <v>7.5</v>
+      <c r="N35" s="6">
+        <v>3.75</v>
       </c>
+      <c r="O35" s="6"/>
     </row>
     <row r="36" spans="1:15" ht="270.75" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
@@ -86737,12 +86768,13 @@
       <c r="L36" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="N36" s="1">
+      <c r="M36" s="1">
         <v>3.25</v>
       </c>
-      <c r="O36" s="8">
-        <v>6.5</v>
+      <c r="N36" s="6">
+        <v>3.25</v>
       </c>
+      <c r="O36" s="6"/>
     </row>
     <row r="37" spans="1:15" ht="213.75" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
@@ -86781,12 +86813,13 @@
       <c r="L37" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="N37" s="1">
+      <c r="M37" s="1">
         <v>16</v>
       </c>
-      <c r="O37" s="8">
-        <v>15</v>
+      <c r="N37" s="6">
+        <v>7.5</v>
       </c>
+      <c r="O37" s="6"/>
     </row>
     <row r="38" spans="1:15" ht="242.25" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
@@ -86825,12 +86858,13 @@
       <c r="L38" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="N38" s="1">
+      <c r="M38" s="1">
         <v>4.25</v>
       </c>
-      <c r="O38" s="8">
-        <v>8.5</v>
+      <c r="N38" s="6">
+        <v>4.25</v>
       </c>
+      <c r="O38" s="6"/>
     </row>
     <row r="39" spans="1:15" ht="213.75" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
@@ -86869,12 +86903,13 @@
       <c r="L39" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="N39" s="1">
+      <c r="M39" s="1">
         <v>11.25</v>
       </c>
-      <c r="O39" s="8">
-        <v>8.25</v>
+      <c r="N39" s="6">
+        <v>4.125</v>
       </c>
+      <c r="O39" s="6"/>
     </row>
     <row r="40" spans="1:15" ht="213.75" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
@@ -86913,12 +86948,13 @@
       <c r="L40" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="N40" s="1">
+      <c r="M40" s="1">
         <v>17</v>
       </c>
-      <c r="O40" s="8">
+      <c r="N40" s="6">
         <v>17</v>
       </c>
+      <c r="O40" s="6"/>
     </row>
     <row r="41" spans="1:15" ht="213.75" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
@@ -86957,12 +86993,13 @@
       <c r="L41" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="N41" s="1">
+      <c r="M41" s="1">
         <v>16</v>
       </c>
-      <c r="O41" s="8">
+      <c r="N41" s="6">
         <v>16</v>
       </c>
+      <c r="O41" s="6"/>
     </row>
     <row r="42" spans="1:15" ht="213.75" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
@@ -87001,12 +87038,13 @@
       <c r="L42" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="N42" s="1">
+      <c r="M42" s="1">
         <v>17</v>
       </c>
-      <c r="O42" s="8">
+      <c r="N42" s="6">
         <v>17</v>
       </c>
+      <c r="O42" s="6"/>
     </row>
     <row r="43" spans="1:15" ht="242.25" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
@@ -87045,12 +87083,13 @@
       <c r="L43" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="N43" s="1">
+      <c r="M43" s="1">
         <v>4.125</v>
       </c>
-      <c r="O43" s="8">
+      <c r="N43" s="6">
         <v>8.25</v>
       </c>
+      <c r="O43" s="6"/>
     </row>
     <row r="44" spans="1:15" ht="213.75" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
@@ -87089,12 +87128,13 @@
       <c r="L44" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="N44" s="1">
+      <c r="M44" s="1">
         <v>17</v>
       </c>
-      <c r="O44" s="8">
+      <c r="N44" s="6">
         <v>17</v>
       </c>
+      <c r="O44" s="6"/>
     </row>
     <row r="45" spans="1:15" ht="213.75" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
@@ -87133,12 +87173,13 @@
       <c r="L45" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="N45" s="1">
+      <c r="M45" s="1">
         <v>14</v>
       </c>
-      <c r="O45" s="8">
+      <c r="N45" s="6">
         <v>13.5</v>
       </c>
+      <c r="O45" s="6"/>
     </row>
     <row r="46" spans="1:15" ht="242.25" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
@@ -87177,12 +87218,13 @@
       <c r="L46" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="N46" s="1">
+      <c r="M46" s="1">
         <v>5.75</v>
       </c>
-      <c r="O46" s="8">
-        <v>11.5</v>
+      <c r="N46" s="6">
+        <v>5.75</v>
       </c>
+      <c r="O46" s="6"/>
     </row>
     <row r="47" spans="1:15" ht="213.75" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
@@ -87221,12 +87263,13 @@
       <c r="L47" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="N47" s="1">
+      <c r="M47" s="1">
         <v>14</v>
       </c>
-      <c r="O47" s="8">
+      <c r="N47" s="6">
         <v>13</v>
       </c>
+      <c r="O47" s="6"/>
     </row>
     <row r="48" spans="1:15" ht="213.75" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
@@ -87265,12 +87308,13 @@
       <c r="L48" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="N48" s="1">
+      <c r="M48" s="1">
         <v>14</v>
       </c>
-      <c r="O48" s="8">
+      <c r="N48" s="6">
         <v>11</v>
       </c>
+      <c r="O48" s="6"/>
     </row>
     <row r="49" spans="1:15" ht="213.75" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
@@ -87309,12 +87353,13 @@
       <c r="L49" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="N49" s="1">
+      <c r="M49" s="1">
         <v>14</v>
       </c>
-      <c r="O49" s="8">
+      <c r="N49" s="6">
         <v>14</v>
       </c>
+      <c r="O49" s="6"/>
     </row>
     <row r="50" spans="1:15" ht="213.75" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
@@ -87353,12 +87398,13 @@
       <c r="L50" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="N50" s="1">
+      <c r="M50" s="1">
         <v>13.75</v>
       </c>
-      <c r="O50" s="8">
-        <v>13.75</v>
+      <c r="N50" s="6">
+        <v>12.55</v>
       </c>
+      <c r="O50" s="6"/>
     </row>
     <row r="51" spans="1:15" ht="213.75" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
@@ -87397,12 +87443,13 @@
       <c r="L51" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="N51" s="1">
+      <c r="M51" s="1">
         <v>17</v>
       </c>
-      <c r="O51" s="8">
+      <c r="N51" s="6">
         <v>16</v>
       </c>
+      <c r="O51" s="6"/>
     </row>
     <row r="52" spans="1:15" ht="213.75" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
@@ -87441,12 +87488,13 @@
       <c r="L52" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="N52" s="1">
+      <c r="M52" s="1">
         <v>17</v>
       </c>
-      <c r="O52" s="8">
+      <c r="N52" s="6">
         <v>17</v>
       </c>
+      <c r="O52" s="6"/>
     </row>
     <row r="53" spans="1:15" ht="213.75" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
@@ -87485,12 +87533,13 @@
       <c r="L53" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="N53" s="1">
+      <c r="M53" s="1">
         <v>14</v>
       </c>
-      <c r="O53" s="8">
+      <c r="N53" s="6">
         <v>9</v>
       </c>
+      <c r="O53" s="6"/>
     </row>
     <row r="54" spans="1:15" ht="213.75" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
@@ -87529,12 +87578,13 @@
       <c r="L54" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="N54" s="1">
+      <c r="M54" s="1">
         <v>17</v>
       </c>
-      <c r="O54" s="8">
+      <c r="N54" s="6">
         <v>17</v>
       </c>
+      <c r="O54" s="6"/>
     </row>
     <row r="55" spans="1:15" ht="213.75" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
@@ -87573,12 +87623,13 @@
       <c r="L55" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="N55" s="1">
+      <c r="M55" s="1">
         <v>15</v>
       </c>
-      <c r="O55" s="8">
-        <v>14</v>
+      <c r="N55" s="6">
+        <v>7</v>
       </c>
+      <c r="O55" s="6"/>
     </row>
     <row r="56" spans="1:15" ht="242.25" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
@@ -87617,12 +87668,13 @@
       <c r="L56" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="N56" s="1">
+      <c r="M56" s="1">
         <v>3.75</v>
       </c>
-      <c r="O56" s="8">
-        <v>6.5</v>
+      <c r="N56" s="6">
+        <v>3.25</v>
       </c>
+      <c r="O56" s="6"/>
     </row>
     <row r="57" spans="1:15" ht="213.75" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
@@ -87661,12 +87713,13 @@
       <c r="L57" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="N57" s="1">
+      <c r="M57" s="1">
         <v>8.5</v>
       </c>
-      <c r="O57" s="8">
+      <c r="N57" s="6">
         <v>9.6</v>
       </c>
+      <c r="O57" s="6"/>
     </row>
     <row r="58" spans="1:15" ht="242.25" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
@@ -87705,12 +87758,13 @@
       <c r="L58" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="N58" s="1">
+      <c r="M58" s="1">
         <v>0.5</v>
       </c>
-      <c r="O58" s="8">
+      <c r="N58" s="6">
         <v>0.5</v>
       </c>
+      <c r="O58" s="6"/>
     </row>
     <row r="59" spans="1:15" ht="242.25" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
@@ -87749,12 +87803,13 @@
       <c r="L59" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="N59" s="1">
+      <c r="M59" s="1">
         <v>12</v>
       </c>
-      <c r="O59" s="8">
+      <c r="N59" s="6">
         <v>12</v>
       </c>
+      <c r="O59" s="6"/>
     </row>
     <row r="60" spans="1:15" ht="242.25" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
@@ -87793,12 +87848,13 @@
       <c r="L60" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="N60" s="1">
+      <c r="M60" s="1">
         <v>0.5</v>
       </c>
-      <c r="O60" s="8">
-        <v>4.5</v>
+      <c r="N60" s="6">
+        <v>2.25</v>
       </c>
+      <c r="O60" s="6"/>
     </row>
     <row r="61" spans="1:15" ht="242.25" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
@@ -87837,12 +87893,13 @@
       <c r="L61" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="N61" s="1">
+      <c r="M61" s="1">
         <v>0.5</v>
       </c>
-      <c r="O61" s="8">
-        <v>4.5</v>
+      <c r="N61" s="6">
+        <v>2.25</v>
       </c>
+      <c r="O61" s="6"/>
     </row>
     <row r="62" spans="1:15" ht="213.75" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
@@ -87881,12 +87938,13 @@
       <c r="L62" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="N62" s="1">
+      <c r="M62" s="1">
         <v>13.75</v>
       </c>
-      <c r="O62" s="1">
+      <c r="N62" s="1">
         <v>14.75</v>
       </c>
+      <c r="O62" s="1"/>
     </row>
     <row r="63" spans="1:15" ht="213.75" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
@@ -87925,12 +87983,13 @@
       <c r="L63" s="4" t="s">
         <v>144</v>
       </c>
+      <c r="M63" s="1">
+        <v>17</v>
+      </c>
       <c r="N63" s="1">
         <v>17</v>
       </c>
-      <c r="O63" s="1">
-        <v>17</v>
-      </c>
+      <c r="O63" s="1"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:L4">
